--- a/Thesis_Results.xlsx
+++ b/Thesis_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/lucia_naviasalva_ufl_edu/Documents/R/MastersThesis2025_git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F4DF45B-AF5A-A34A-9052-6C546960D09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{2F4DF45B-AF5A-A34A-9052-6C546960D09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F02DC9F-0C6A-684C-9AAF-709A11A7E67E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="32100" windowHeight="19700" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="160" yWindow="940" windowWidth="14460" windowHeight="19620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OldResults" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="184">
   <si>
     <t>Hypotheses</t>
   </si>
@@ -486,31 +486,10 @@
     <t>2 - Density Dependence - Part 2</t>
   </si>
   <si>
-    <t>Ach all rounds</t>
-  </si>
-  <si>
-    <t>ach_2_DD &lt;- glmmTMB(cbind(alive_n, density - alive_n) ~ 0 + density:burn:as.factor(round) + (1 | block/cage), family = binomial, data = cage_exp_allrounds %&gt;% filter(dep == "monoculture", sp == "ach"))</t>
-  </si>
-  <si>
-    <t>Ach round 5</t>
-  </si>
-  <si>
-    <t>ach_2_DD_5 &lt;- glmmTMB(cbind(alive_n, density - alive_n) ~ density * burn + (1 | block/cage), family = binomial, data = cage_exp_allrounds %&gt;% filter(dep == "monoculture", sp == "ach", round == 5))</t>
-  </si>
-  <si>
-    <t>Apt round 5</t>
-  </si>
-  <si>
     <t>apt_2_DD_5 &lt;- glmmTMB(cbind(alive_n, density - alive_n) ~ density * burn + (1 | block/cage), family = binomial, data = cage_exp_allrounds %&gt;% filter(dep == "monoculture", sp == "apt", round == 5))</t>
   </si>
   <si>
     <t>3 - Frequency Dependence - Part 2</t>
-  </si>
-  <si>
-    <t>ach_2_FD &lt;- glmmTMB(perc_survival ~ grass_perc * trt * burn, data = surv_plant %&gt;% filter(sp == "ach", trt != "ach_low", round == 5), family = "ordbeta")</t>
-  </si>
-  <si>
-    <t>apt_2_fd &lt;- glmmTMB(perc_survival ~ grass_perc * trt * burn, data = surv_plant %&gt;% filter(sp == "apt", trt != "apt_low", round == 5, trt != "control"), family = "ordbeta")</t>
   </si>
   <si>
     <t xml:space="preserve">trt        0.3510  1     0.5535    
@@ -856,6 +835,466 @@
   </si>
   <si>
     <t xml:space="preserve">emmeans not significant, so I'm not sure if I can talk about this. Already talked about grass % in density dependence, so maybe that's it? </t>
+  </si>
+  <si>
+    <t>Although the simple slopes within individual burn and density treatments were mostly not significant, the visual pattern and estimated trends suggested that survival of A. carinatum generally increased with greater grass cover, whereas survival of A. sphenarioides generally declined as grass cover increased [HP1.1](Figure 2).</t>
+  </si>
+  <si>
+    <t>ach_2_DD &lt;- glmmTMB(perc_survival ~ density * burn * as.factor(round) + (1 | block/cage),
+      family = "ordbeta", data = cages_2 %&gt;%
+       filter(dep == "monoculture", sp == "ach", trt != "control",  round &gt; 3))</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">density                        0.0590  1  0.8080746    
+burn                           0.0088  1  0.9252710    
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>as.factor(round)              14.0333  2  0.0008968 ***</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">density:burn                   6.3706  1  0.0116025 *  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+density:as.factor(round)       1.8295  2  0.4006241    
+burn:as.factor(round)          2.1923  2  0.3341568    
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>density:burn:as.factor(round) 11.5247  2  0.0031438 **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EMTRENDS
+ round burn density.trend    SE  df asymp.LCL asymp.UCL z.ratio p.value
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">     4 b           0.5085 0.195 Inf     0.126    0.8907   2.607  0.0091</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">     5 b           0.4341 0.156 Inf     0.128    0.7405   2.777  0.0055</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+     6 b           0.0755 0.147 Inf    -0.213    0.3640   0.513  0.6083
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">    4 u          -0.2196 0.101 Inf    -0.417   -0.0225  -2.183  0.0290</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+     5 u          -0.1158 0.105 Inf    -0.321    0.0894  -1.106  0.2688
+     6 u          -0.0183 0.109 Inf    -0.232    0.1952  -0.168  0.8664</t>
+    </r>
+  </si>
+  <si>
+    <t>Apt r3-6</t>
+  </si>
+  <si>
+    <t>Ach r3-6</t>
+  </si>
+  <si>
+    <t>ach_2_fd &lt;- glmmTMB(perc_survival ~ trt * burn * as.factor(round) + (1|block/cage),
+                    data = cages_2 %&gt;% 
+                      filter(sp == "ach", trt != "ach_low"), family = "ordbeta")</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">density                        3.4643  1   0.062706 . </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+burn                           1.7574  1   0.184953   
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>as.factor(round)              13.6479  2   0.001087 **</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+density:burn                   0.0141  1   0.905359   
+density:as.factor(round)       1.0879  2   0.580452   
+burn:as.factor(round)          2.0039  2   0.367161   
+density:burn:as.factor(round)  1.1178  2   0.571835 </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">trt                        3.4517  2   0.178020    
+burn                       0.1534  1   0.695292    
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>as.factor(round)          25.9426  2  2.326e-06 ***</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+trt:burn                   0.6865  2   0.709453    
+trt:as.factor(round)       4.0122  4   0.404352    
+burn:as.factor(round)      0.3110  2   0.855973    
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">trt:burn:as.factor(round) 14.4923  4   0.005879 ** </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EMTRENDS
+ round burn density.trend    SE  df asymp.LCL asymp.UCL z.ratio p.value
+     4 b           -0.229 0.221 Inf    -0.662   0.20473  -1.034  0.3010
+     5 b           -0.205 0.194 Inf    -0.584   0.17480  -1.057  0.2905
+    </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> 6 b           -0.435 0.223 Inf    -0.873   0.00234  -1.949  0.0512</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+     4 u           -0.185 0.210 Inf    -0.597   0.22732  -0.879  0.3791
+     5 u           -0.273 0.212 Inf    -0.688   0.14256  -1.287  0.1980
+     6 u           -0.262 0.219 Inf    -0.690   0.16660  -1.198  0.2310</t>
+    </r>
+  </si>
+  <si>
+    <t>apt_2_fd &lt;- glmmTMB(perc_survival ~ trt * burn * as.factor(round) + (1|block/cage), data = cages_2 %&gt;%  filter(sp == "apt", trt != "apt_low", trt != "control") %&gt;%  filter(round &gt; 3), family = "ordbeta")</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">trt                        2.1211  2  0.3462708    
+burn                       0.0519  1  0.8197488    
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>as.factor(round)          16.8541  2  0.0002189 ***</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">trt:burn                   5.1695  2  0.0754163 .  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+trt:as.factor(round)       2.1249  4  0.7128062    
+burn:as.factor(round)      0.6431  2  0.7250409    
+trt:burn:as.factor(round)  4.5670  4  0.3346778  </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>burn = b:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        0.317 0.183 Inf    1  -1.990  0.1147
+ ach_33 / apt_high      0.700 0.363 Inf    1  -0.689  0.7702
+ ach_66 / apt_high      2.208 1.340 Inf    1   1.304  0.3931
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>burn = u:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        1.501 0.779 Inf    1   0.782  0.7139
+ ach_33 / apt_high      2.582 1.400 Inf    1   1.756  0.1846
+ ach_66 / apt_high      1.721 0.938 Inf    1   0.996  0.5795
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>burn = b:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.398 0.0824 Inf     0.252     0.565
+ ach_66      0.676 0.1030 Inf     0.453     0.840
+ apt_high    0.486 0.0970 Inf     0.306     0.669
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>burn = u:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.601 0.0873 Inf     0.424     0.755
+ ach_66      0.501 0.0932 Inf     0.326     0.676
+ apt_high    0.368 0.0928 Inf     0.211     0.560</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Grass cover not used because I's not as biologically relevant </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">burn = b, round = 4:
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        2.504 1.660 Inf    1   1.384  0.3494
+ ach_33 / ach_high      1.576 1.100 Inf    1   0.650  0.7923
+ ach_66 / ach_high      0.630 0.404 Inf    1  -0.722  0.7506
+burn = u, round = 4:
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        0.623 0.469 Inf    1  -0.628  0.8048
+ ach_33 / ach_high      3.618 2.870 Inf    1   1.621  0.2369
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> ach_66 / ach_high      5.803 4.390 Inf    1   2.325  0.0524</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve">
+burn = b, round = 5:
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        2.573 1.630 Inf    1   1.497  0.2924
+ ach_33 / ach_high      2.399 1.560 Inf    1   1.342  0.3720
+ ach_66 / ach_high      0.932 0.553 Inf    1  -0.118  0.9923
+burn = u, round = 5:
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        2.103 1.500 Inf    1   1.043  0.5498
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> ach_33 / ach_high      4.755 3.600 Inf    1   2.058  0.0988
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t xml:space="preserve"> ach_66 / ach_high      2.260 1.510 Inf    1   1.219  0.4417
+burn = b, round = 6:
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        2.319 1.530 Inf    1   1.274  0.4098
+ ach_33 / ach_high      3.737 2.760 Inf    1   1.782  0.1756
+ ach_66 / ach_high      1.611 1.040 Inf    1   0.741  0.7393
+burn = u, round = 6:
+ contrast          odds.ratio    SE  df null z.ratio p.value
+ ach_33 / ach_66        1.675 1.220 Inf    1   0.707  0.7591
+ ach_33 / ach_high      0.900 0.683 Inf    1  -0.139  0.9894
+ ach_66 / ach_high      0.537 0.369 Inf    1  -0.904  0.6379</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1151,7 +1590,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1368,6 +1807,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2517,14 +2962,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" style="64" customWidth="1"/>
     <col min="2" max="2" width="14" style="64" customWidth="1"/>
     <col min="3" max="3" width="80" style="64" customWidth="1"/>
-    <col min="4" max="4" width="36.83203125" style="66" customWidth="1"/>
-    <col min="5" max="5" width="66.33203125" style="64" customWidth="1"/>
+    <col min="4" max="4" width="52" style="66" customWidth="1"/>
+    <col min="5" max="5" width="75.6640625" style="64" customWidth="1"/>
     <col min="6" max="6" width="52" style="66" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="8.83203125" style="64"/>
   </cols>
@@ -2543,10 +2988,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="62" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F1" s="72" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
@@ -2560,7 +3005,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="65" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E2" s="65"/>
     </row>
@@ -2575,7 +3020,7 @@
         <v>25</v>
       </c>
       <c r="D3" s="65" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E3" s="65"/>
     </row>
@@ -2590,10 +3035,10 @@
         <v>39</v>
       </c>
       <c r="D4" s="65" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E4" s="67" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="352" customHeight="1" x14ac:dyDescent="0.2">
@@ -2604,13 +3049,13 @@
         <v>144</v>
       </c>
       <c r="C5" s="68" t="s">
+        <v>153</v>
+      </c>
+      <c r="D5" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="68" t="s">
         <v>160</v>
-      </c>
-      <c r="D5" s="68" t="s">
-        <v>161</v>
-      </c>
-      <c r="E5" s="68" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="170" customHeight="1" x14ac:dyDescent="0.2">
@@ -2621,13 +3066,16 @@
         <v>59</v>
       </c>
       <c r="C6" s="68" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D6" s="68" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E6" s="68" t="s">
-        <v>166</v>
+        <v>159</v>
+      </c>
+      <c r="F6" s="66" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="384" customHeight="1" x14ac:dyDescent="0.2">
@@ -2638,16 +3086,16 @@
         <v>144</v>
       </c>
       <c r="C7" s="69" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="D7" s="69" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E7" s="69" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="197" customHeight="1" x14ac:dyDescent="0.2">
@@ -2658,82 +3106,88 @@
         <v>59</v>
       </c>
       <c r="C8" s="69" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D8" s="69" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="E8" s="69" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G8" s="64" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="139" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="70" t="s">
         <v>146</v>
       </c>
       <c r="B9" s="70" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="70" t="s">
-        <v>148</v>
-      </c>
-      <c r="D9" s="70"/>
-      <c r="E9" s="70"/>
-    </row>
-    <row r="10" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>174</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="70" t="s">
+        <v>171</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>172</v>
+      </c>
+      <c r="F9" s="66" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="152" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="70" t="s">
         <v>146</v>
       </c>
       <c r="B10" s="70" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="C10" s="70" t="s">
-        <v>150</v>
-      </c>
-      <c r="D10" s="70"/>
-      <c r="E10" s="70"/>
-    </row>
-    <row r="11" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="70" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="70" t="s">
-        <v>151</v>
-      </c>
-      <c r="C11" s="70" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="70"/>
-      <c r="E11" s="70"/>
-    </row>
-    <row r="12" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
+        <v>147</v>
+      </c>
+      <c r="D10" s="70" t="s">
+        <v>176</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="71" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="71" t="s">
+        <v>177</v>
+      </c>
+      <c r="E11" s="71" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="71" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B12" s="71" t="s">
-        <v>144</v>
-      </c>
-      <c r="C12" s="71" t="s">
-        <v>154</v>
-      </c>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-    </row>
-    <row r="13" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="71" t="s">
-        <v>153</v>
-      </c>
-      <c r="B13" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="71" t="s">
-        <v>155</v>
-      </c>
-      <c r="D13" s="71"/>
-      <c r="E13" s="71"/>
+      <c r="C12" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>180</v>
+      </c>
+      <c r="E12" s="71" t="s">
+        <v>181</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Thesis_Results.xlsx
+++ b/Thesis_Results.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uflorida-my.sharepoint.com/personal/lucia_naviasalva_ufl_edu/Documents/R/MastersThesis2025_git/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="75" documentId="8_{2F4DF45B-AF5A-A34A-9052-6C546960D09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1F02DC9F-0C6A-684C-9AAF-709A11A7E67E}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="8_{2F4DF45B-AF5A-A34A-9052-6C546960D09A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5E316D5-271A-AB40-B5C8-D8205125C352}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="940" windowWidth="14460" windowHeight="19620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="140" yWindow="780" windowWidth="12860" windowHeight="19580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OldResults" sheetId="1" r:id="rId1"/>
     <sheet name="Current Results Template" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -1293,7 +1292,37 @@
  contrast          odds.ratio    SE  df null z.ratio p.value
  ach_33 / ach_66        1.675 1.220 Inf    1   0.707  0.7591
  ach_33 / ach_high      0.900 0.683 Inf    1  -0.139  0.9894
- ach_66 / ach_high      0.537 0.369 Inf    1  -0.904  0.6379</t>
+ ach_66 / ach_high      0.537 0.369 Inf    1  -0.904  0.6379
+burn = b, round = 4:
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.718 0.1050 Inf    0.4802     0.876
+ ach_66      0.505 0.1050 Inf    0.3087     0.699
+ ach_high    0.618 0.1150 Inf    0.3847     0.807
+burn = u, round = 4:
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.639 0.1320 Inf    0.3653     0.845
+ ach_66      0.739 0.0994 Inf    0.5080     0.886
+ ach_high    0.328 0.1230 Inf    0.1409     0.593
+burn = b, round = 5:
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.668 0.1090 Inf    0.4348     0.840
+ ach_66      0.438 0.0999 Inf    0.2605     0.633
+ ach_high    0.456 0.1080 Inf    0.2635     0.662
+burn = u, round = 5:
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.649 0.1280 Inf    0.3798     0.848
+ ach_66      0.468 0.1090 Inf    0.2720     0.674
+ ach_high    0.280 0.1020 Inf    0.1257     0.512
+burn = b, round = 6:
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.493 0.1310 Inf    0.2580     0.731
+ ach_66      0.295 0.0830 Inf    0.1611     0.478
+ ach_high    0.207 0.0834 Inf    0.0876     0.414
+burn = u, round = 6:
+ trt      response     SE  df asymp.LCL asymp.UCL
+ ach_33      0.336 0.1260 Inf    0.1429     0.605
+ ach_66      0.232 0.0829 Inf    0.1081     0.429
+ ach_high    0.360 0.1170 Inf    0.1723     0.603</t>
     </r>
   </si>
 </sst>
@@ -1685,96 +1714,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1813,6 +1752,96 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2004,10 +2033,10 @@
       <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="41"/>
+      <c r="F1" s="68"/>
     </row>
     <row r="2" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
@@ -2022,10 +2051,10 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="42" t="s">
+      <c r="E2" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="43"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
@@ -2034,10 +2063,10 @@
       <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="44" t="s">
+      <c r="E3" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="45"/>
+      <c r="F3" s="72"/>
     </row>
     <row r="4" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
@@ -2046,110 +2075,110 @@
       <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="47"/>
+      <c r="F4" s="74"/>
     </row>
     <row r="5" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="33"/>
+      <c r="F5" s="60"/>
     </row>
     <row r="6" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
       <c r="D6" s="6"/>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="35"/>
+      <c r="F6" s="52"/>
     </row>
     <row r="7" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="33"/>
+      <c r="F7" s="60"/>
     </row>
     <row r="8" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="33"/>
+      <c r="F8" s="60"/>
     </row>
     <row r="9" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
-      <c r="E9" s="34" t="s">
+      <c r="E9" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="F9" s="35"/>
+      <c r="F9" s="52"/>
     </row>
     <row r="10" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="33"/>
+      <c r="F10" s="60"/>
     </row>
     <row r="11" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="33"/>
+      <c r="F11" s="60"/>
     </row>
     <row r="12" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
-      <c r="E12" s="34" t="s">
+      <c r="E12" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="35"/>
+      <c r="F12" s="52"/>
     </row>
     <row r="13" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="33"/>
+      <c r="F13" s="60"/>
     </row>
     <row r="14" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A14" s="19"/>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="36" t="s">
+      <c r="E14" s="61" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="37"/>
+      <c r="F14" s="62"/>
     </row>
     <row r="15" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -2164,10 +2193,10 @@
       <c r="D15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="38" t="s">
+      <c r="E15" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="F15" s="39"/>
+      <c r="F15" s="48"/>
     </row>
     <row r="16" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
@@ -2176,10 +2205,10 @@
       <c r="D16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="33"/>
+      <c r="F16" s="60"/>
     </row>
     <row r="17" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
@@ -2188,76 +2217,76 @@
       <c r="D17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="F17" s="33"/>
+      <c r="F17" s="60"/>
     </row>
     <row r="18" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A18" s="9"/>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="F18" s="35"/>
+      <c r="F18" s="52"/>
     </row>
     <row r="19" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A19" s="9"/>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="33"/>
+      <c r="F19" s="60"/>
     </row>
     <row r="20" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A20" s="9"/>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="59" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="33"/>
+      <c r="F20" s="60"/>
     </row>
     <row r="21" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A21" s="9"/>
-      <c r="E21" s="34" t="s">
+      <c r="E21" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="F21" s="35"/>
+      <c r="F21" s="52"/>
     </row>
     <row r="22" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="9"/>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="F22" s="33"/>
+      <c r="F22" s="60"/>
     </row>
     <row r="23" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A23" s="9"/>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="F23" s="33"/>
+      <c r="F23" s="60"/>
     </row>
     <row r="24" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A24" s="9"/>
-      <c r="E24" s="34" t="s">
+      <c r="E24" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="35"/>
+      <c r="F24" s="52"/>
     </row>
     <row r="25" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A25" s="9"/>
-      <c r="E25" s="32" t="s">
+      <c r="E25" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="33"/>
+      <c r="F25" s="60"/>
     </row>
     <row r="26" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A26" s="14"/>
       <c r="B26" s="15"/>
       <c r="C26" s="15"/>
       <c r="D26" s="15"/>
-      <c r="E26" s="36" t="s">
+      <c r="E26" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="F26" s="37"/>
+      <c r="F26" s="62"/>
     </row>
     <row r="27" spans="1:6" ht="44" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
@@ -2272,30 +2301,30 @@
       <c r="D27" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="F27" s="49"/>
+      <c r="F27" s="66"/>
     </row>
     <row r="28" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
       <c r="B28" s="6"/>
       <c r="C28" s="7"/>
       <c r="D28" s="10"/>
-      <c r="E28" s="32" t="s">
+      <c r="E28" s="59" t="s">
         <v>42</v>
       </c>
-      <c r="F28" s="33"/>
+      <c r="F28" s="60"/>
     </row>
     <row r="29" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A29" s="19"/>
       <c r="B29" s="20"/>
       <c r="C29" s="24"/>
       <c r="D29" s="25"/>
-      <c r="E29" s="36" t="s">
+      <c r="E29" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="F29" s="37"/>
+      <c r="F29" s="62"/>
     </row>
     <row r="30" spans="1:6" ht="46" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
@@ -2310,10 +2339,10 @@
       <c r="D30" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="38" t="s">
+      <c r="E30" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="F30" s="39"/>
+      <c r="F30" s="48"/>
     </row>
     <row r="31" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
@@ -2324,10 +2353,10 @@
       <c r="D31" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="59" t="s">
         <v>51</v>
       </c>
-      <c r="F31" s="33"/>
+      <c r="F31" s="60"/>
     </row>
     <row r="32" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
@@ -2338,10 +2367,10 @@
       <c r="D32" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E32" s="32" t="s">
+      <c r="E32" s="59" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="33"/>
+      <c r="F32" s="60"/>
     </row>
     <row r="33" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A33" s="5"/>
@@ -2349,28 +2378,28 @@
       <c r="D33" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E33" s="34" t="s">
+      <c r="E33" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F33" s="35"/>
+      <c r="F33" s="52"/>
     </row>
     <row r="34" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A34" s="5"/>
       <c r="B34" s="6"/>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="59" t="s">
         <v>57</v>
       </c>
-      <c r="F34" s="33"/>
+      <c r="F34" s="60"/>
     </row>
     <row r="35" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A35" s="28"/>
       <c r="B35" s="29"/>
       <c r="C35" s="30"/>
       <c r="D35" s="30"/>
-      <c r="E35" s="50" t="s">
+      <c r="E35" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="F35" s="51"/>
+      <c r="F35" s="64"/>
     </row>
     <row r="36" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
@@ -2383,10 +2412,10 @@
       <c r="D36" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="E36" s="34" t="s">
+      <c r="E36" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="F36" s="35"/>
+      <c r="F36" s="52"/>
     </row>
     <row r="37" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
@@ -2397,10 +2426,10 @@
       <c r="D37" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="E37" s="32" t="s">
+      <c r="E37" s="59" t="s">
         <v>63</v>
       </c>
-      <c r="F37" s="33"/>
+      <c r="F37" s="60"/>
     </row>
     <row r="38" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
@@ -2410,37 +2439,37 @@
       <c r="D38" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E38" s="32" t="s">
+      <c r="E38" s="59" t="s">
         <v>66</v>
       </c>
-      <c r="F38" s="33"/>
+      <c r="F38" s="60"/>
     </row>
     <row r="39" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="D39" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E39" s="34" t="s">
+      <c r="E39" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F39" s="35"/>
+      <c r="F39" s="52"/>
     </row>
     <row r="40" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
-      <c r="E40" s="32" t="s">
+      <c r="E40" s="59" t="s">
         <v>68</v>
       </c>
-      <c r="F40" s="33"/>
+      <c r="F40" s="60"/>
     </row>
     <row r="41" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A41" s="19"/>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
       <c r="D41" s="15"/>
-      <c r="E41" s="36" t="s">
+      <c r="E41" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="F41" s="37"/>
+      <c r="F41" s="62"/>
     </row>
     <row r="42" spans="1:6" ht="46" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
@@ -2455,10 +2484,10 @@
       <c r="D42" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E42" s="38" t="s">
+      <c r="E42" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="F42" s="39"/>
+      <c r="F42" s="48"/>
     </row>
     <row r="43" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A43" s="9"/>
@@ -2468,10 +2497,10 @@
       <c r="D43" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E43" s="32" t="s">
+      <c r="E43" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="F43" s="33"/>
+      <c r="F43" s="60"/>
     </row>
     <row r="44" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A44" s="9"/>
@@ -2481,10 +2510,10 @@
       <c r="D44" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="32" t="s">
+      <c r="E44" s="59" t="s">
         <v>77</v>
       </c>
-      <c r="F44" s="33"/>
+      <c r="F44" s="60"/>
     </row>
     <row r="45" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A45" s="9"/>
@@ -2492,41 +2521,41 @@
       <c r="D45" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E45" s="32" t="s">
+      <c r="E45" s="59" t="s">
         <v>79</v>
       </c>
-      <c r="F45" s="33"/>
+      <c r="F45" s="60"/>
     </row>
     <row r="46" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A46" s="9"/>
-      <c r="E46" s="34" t="s">
+      <c r="E46" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F46" s="35"/>
+      <c r="F46" s="52"/>
     </row>
     <row r="47" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
-      <c r="E47" s="32" t="s">
+      <c r="E47" s="59" t="s">
         <v>80</v>
       </c>
-      <c r="F47" s="33"/>
+      <c r="F47" s="60"/>
     </row>
     <row r="48" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A48" s="9"/>
-      <c r="E48" s="32" t="s">
+      <c r="E48" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="F48" s="33"/>
+      <c r="F48" s="60"/>
     </row>
     <row r="49" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A49" s="31"/>
       <c r="B49" s="30"/>
       <c r="C49" s="30"/>
       <c r="D49" s="30"/>
-      <c r="E49" s="50" t="s">
+      <c r="E49" s="63" t="s">
         <v>82</v>
       </c>
-      <c r="F49" s="51"/>
+      <c r="F49" s="64"/>
     </row>
     <row r="50" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A50" s="9"/>
@@ -2539,10 +2568,10 @@
       <c r="D50" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E50" s="34" t="s">
+      <c r="E50" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="F50" s="35"/>
+      <c r="F50" s="52"/>
     </row>
     <row r="51" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A51" s="9"/>
@@ -2552,10 +2581,10 @@
       <c r="D51" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E51" s="32" t="s">
+      <c r="E51" s="59" t="s">
         <v>86</v>
       </c>
-      <c r="F51" s="33"/>
+      <c r="F51" s="60"/>
     </row>
     <row r="52" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
@@ -2565,51 +2594,51 @@
       <c r="D52" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E52" s="32" t="s">
+      <c r="E52" s="59" t="s">
         <v>89</v>
       </c>
-      <c r="F52" s="33"/>
+      <c r="F52" s="60"/>
     </row>
     <row r="53" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
       <c r="D53" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E53" s="32" t="s">
+      <c r="E53" s="59" t="s">
         <v>91</v>
       </c>
-      <c r="F53" s="33"/>
+      <c r="F53" s="60"/>
     </row>
     <row r="54" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A54" s="9"/>
-      <c r="E54" s="34" t="s">
+      <c r="E54" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F54" s="35"/>
+      <c r="F54" s="52"/>
     </row>
     <row r="55" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A55" s="9"/>
-      <c r="E55" s="32" t="s">
+      <c r="E55" s="59" t="s">
         <v>92</v>
       </c>
-      <c r="F55" s="33"/>
+      <c r="F55" s="60"/>
     </row>
     <row r="56" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A56" s="9"/>
-      <c r="E56" s="32" t="s">
+      <c r="E56" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="F56" s="33"/>
+      <c r="F56" s="60"/>
     </row>
     <row r="57" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A57" s="14"/>
       <c r="B57" s="15"/>
       <c r="C57" s="15"/>
       <c r="D57" s="15"/>
-      <c r="E57" s="36" t="s">
+      <c r="E57" s="61" t="s">
         <v>94</v>
       </c>
-      <c r="F57" s="37"/>
+      <c r="F57" s="62"/>
     </row>
     <row r="58" spans="1:6" ht="46" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
@@ -2624,10 +2653,10 @@
       <c r="D58" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="E58" s="38" t="s">
+      <c r="E58" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="F58" s="39"/>
+      <c r="F58" s="48"/>
     </row>
     <row r="59" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A59" s="5"/>
@@ -2638,10 +2667,10 @@
       <c r="D59" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E59" s="54" t="s">
+      <c r="E59" s="49" t="s">
         <v>100</v>
       </c>
-      <c r="F59" s="55"/>
+      <c r="F59" s="50"/>
     </row>
     <row r="60" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A60" s="5"/>
@@ -2652,38 +2681,38 @@
       <c r="D60" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="E60" s="54" t="s">
+      <c r="E60" s="49" t="s">
         <v>103</v>
       </c>
-      <c r="F60" s="55"/>
+      <c r="F60" s="50"/>
     </row>
     <row r="61" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A61" s="5"/>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
       <c r="D61" s="6"/>
-      <c r="E61" s="34" t="s">
+      <c r="E61" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F61" s="35"/>
+      <c r="F61" s="52"/>
     </row>
     <row r="62" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A62" s="5"/>
       <c r="B62" s="6"/>
-      <c r="E62" s="54" t="s">
+      <c r="E62" s="49" t="s">
         <v>104</v>
       </c>
-      <c r="F62" s="55"/>
+      <c r="F62" s="50"/>
     </row>
     <row r="63" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A63" s="28"/>
       <c r="B63" s="29"/>
       <c r="C63" s="30"/>
       <c r="D63" s="30"/>
-      <c r="E63" s="56" t="s">
+      <c r="E63" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="F63" s="57"/>
+      <c r="F63" s="54"/>
     </row>
     <row r="64" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
@@ -2696,10 +2725,10 @@
       <c r="D64" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E64" s="54" t="s">
+      <c r="E64" s="49" t="s">
         <v>108</v>
       </c>
-      <c r="F64" s="55"/>
+      <c r="F64" s="50"/>
     </row>
     <row r="65" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
@@ -2710,10 +2739,10 @@
       <c r="D65" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E65" s="54" t="s">
+      <c r="E65" s="49" t="s">
         <v>111</v>
       </c>
-      <c r="F65" s="55"/>
+      <c r="F65" s="50"/>
     </row>
     <row r="66" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A66" s="19"/>
@@ -2724,10 +2753,10 @@
       <c r="D66" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="E66" s="52" t="s">
+      <c r="E66" s="57" t="s">
         <v>114</v>
       </c>
-      <c r="F66" s="53"/>
+      <c r="F66" s="58"/>
     </row>
     <row r="67" spans="1:6" ht="46" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
@@ -2742,10 +2771,10 @@
       <c r="D67" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="E67" s="38" t="s">
+      <c r="E67" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="F67" s="39"/>
+      <c r="F67" s="48"/>
     </row>
     <row r="68" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A68" s="9"/>
@@ -2755,10 +2784,10 @@
       <c r="D68" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E68" s="54" t="s">
+      <c r="E68" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="F68" s="55"/>
+      <c r="F68" s="50"/>
     </row>
     <row r="69" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A69" s="9"/>
@@ -2768,60 +2797,60 @@
       <c r="D69" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E69" s="54" t="s">
+      <c r="E69" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="F69" s="55"/>
+      <c r="F69" s="50"/>
     </row>
     <row r="70" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A70" s="9"/>
       <c r="D70" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="E70" s="54" t="s">
+      <c r="E70" s="49" t="s">
         <v>124</v>
       </c>
-      <c r="F70" s="55"/>
+      <c r="F70" s="50"/>
     </row>
     <row r="71" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A71" s="9"/>
       <c r="D71" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E71" s="34" t="s">
+      <c r="E71" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="F71" s="35"/>
+      <c r="F71" s="52"/>
     </row>
     <row r="72" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A72" s="9"/>
       <c r="D72" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="E72" s="54" t="s">
+      <c r="E72" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="F72" s="55"/>
+      <c r="F72" s="50"/>
     </row>
     <row r="73" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A73" s="9"/>
       <c r="D73" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E73" s="54" t="s">
+      <c r="E73" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="F73" s="55"/>
+      <c r="F73" s="50"/>
     </row>
     <row r="74" spans="1:6" ht="22" x14ac:dyDescent="0.2">
       <c r="A74" s="31"/>
       <c r="B74" s="30"/>
       <c r="C74" s="30"/>
       <c r="D74" s="30"/>
-      <c r="E74" s="56" t="s">
+      <c r="E74" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="F74" s="57"/>
+      <c r="F74" s="54"/>
     </row>
     <row r="75" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A75" s="9"/>
@@ -2834,10 +2863,10 @@
       <c r="D75" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E75" s="60" t="s">
+      <c r="E75" s="55" t="s">
         <v>133</v>
       </c>
-      <c r="F75" s="61"/>
+      <c r="F75" s="56"/>
     </row>
     <row r="76" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A76" s="9"/>
@@ -2847,10 +2876,10 @@
       <c r="D76" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="E76" s="60" t="s">
+      <c r="E76" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="F76" s="61"/>
+      <c r="F76" s="56"/>
     </row>
     <row r="77" spans="1:6" ht="24" x14ac:dyDescent="0.2">
       <c r="A77" s="9"/>
@@ -2860,10 +2889,10 @@
       <c r="D77" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E77" s="60" t="s">
+      <c r="E77" s="55" t="s">
         <v>138</v>
       </c>
-      <c r="F77" s="61"/>
+      <c r="F77" s="56"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="14"/>
@@ -2872,59 +2901,25 @@
       <c r="D78" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="E78" s="58"/>
-      <c r="F78" s="59"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="78">
-    <mergeCell ref="E78:F78"/>
-    <mergeCell ref="E67:F67"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="E71:F71"/>
-    <mergeCell ref="E72:F72"/>
-    <mergeCell ref="E73:F73"/>
-    <mergeCell ref="E74:F74"/>
-    <mergeCell ref="E75:F75"/>
-    <mergeCell ref="E76:F76"/>
-    <mergeCell ref="E77:F77"/>
-    <mergeCell ref="E66:F66"/>
-    <mergeCell ref="E55:F55"/>
-    <mergeCell ref="E56:F56"/>
-    <mergeCell ref="E57:F57"/>
-    <mergeCell ref="E58:F58"/>
-    <mergeCell ref="E59:F59"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="E63:F63"/>
-    <mergeCell ref="E64:F64"/>
-    <mergeCell ref="E65:F65"/>
-    <mergeCell ref="E54:F54"/>
-    <mergeCell ref="E43:F43"/>
-    <mergeCell ref="E44:F44"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="E51:F51"/>
-    <mergeCell ref="E52:F52"/>
-    <mergeCell ref="E53:F53"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E35:F35"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="E30:F30"/>
@@ -2939,22 +2934,56 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="E29:F29"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="E17:F17"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="E35:F35"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E54:F54"/>
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="E51:F51"/>
+    <mergeCell ref="E52:F52"/>
+    <mergeCell ref="E53:F53"/>
+    <mergeCell ref="E66:F66"/>
+    <mergeCell ref="E55:F55"/>
+    <mergeCell ref="E56:F56"/>
+    <mergeCell ref="E57:F57"/>
+    <mergeCell ref="E58:F58"/>
+    <mergeCell ref="E59:F59"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="E63:F63"/>
+    <mergeCell ref="E64:F64"/>
+    <mergeCell ref="E65:F65"/>
+    <mergeCell ref="E78:F78"/>
+    <mergeCell ref="E67:F67"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="E71:F71"/>
+    <mergeCell ref="E72:F72"/>
+    <mergeCell ref="E73:F73"/>
+    <mergeCell ref="E74:F74"/>
+    <mergeCell ref="E75:F75"/>
+    <mergeCell ref="E76:F76"/>
+    <mergeCell ref="E77:F77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2965,133 +2994,133 @@
   <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" style="64" customWidth="1"/>
-    <col min="2" max="2" width="14" style="64" customWidth="1"/>
-    <col min="3" max="3" width="80" style="64" customWidth="1"/>
-    <col min="4" max="4" width="52" style="66" customWidth="1"/>
-    <col min="5" max="5" width="75.6640625" style="64" customWidth="1"/>
-    <col min="6" max="6" width="52" style="66" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.83203125" style="64"/>
+    <col min="1" max="1" width="13.5" style="34" customWidth="1"/>
+    <col min="2" max="2" width="14" style="34" customWidth="1"/>
+    <col min="3" max="3" width="80" style="34" customWidth="1"/>
+    <col min="4" max="4" width="52" style="36" customWidth="1"/>
+    <col min="5" max="5" width="75.6640625" style="34" customWidth="1"/>
+    <col min="6" max="6" width="52" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="34"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="62" t="s">
+      <c r="B1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="62" t="s">
+      <c r="C1" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="D1" s="63" t="s">
+      <c r="D1" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="62" t="s">
+      <c r="E1" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="72" t="s">
+      <c r="F1" s="42" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="B2" s="65" t="s">
+      <c r="B2" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="65" t="s">
+      <c r="D2" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="E2" s="65"/>
+      <c r="E2" s="35"/>
     </row>
     <row r="3" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="65" t="s">
+      <c r="B3" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="35" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="E3" s="65"/>
+      <c r="E3" s="35"/>
     </row>
     <row r="4" spans="1:7" ht="56" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="65" t="s">
+      <c r="B4" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="65" t="s">
+      <c r="C4" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="65" t="s">
+      <c r="D4" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="E4" s="67" t="s">
+      <c r="E4" s="37" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="352" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="68" t="s">
+      <c r="B5" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="C5" s="68" t="s">
+      <c r="C5" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="38" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="68" t="s">
+      <c r="E5" s="38" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="170" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="38" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="68" t="s">
+      <c r="C6" s="38" t="s">
         <v>158</v>
       </c>
-      <c r="D6" s="68" t="s">
+      <c r="D6" s="38" t="s">
         <v>155</v>
       </c>
-      <c r="E6" s="68" t="s">
+      <c r="E6" s="38" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="36" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="384" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="69" t="s">
+      <c r="A7" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="39" t="s">
         <v>167</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="39" t="s">
         <v>161</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="39" t="s">
         <v>162</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -3099,93 +3128,93 @@
       </c>
     </row>
     <row r="8" spans="1:7" ht="197" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="39" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="69" t="s">
+      <c r="C8" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="D8" s="69" t="s">
+      <c r="D8" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="E8" s="69" t="s">
+      <c r="E8" s="39" t="s">
         <v>165</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="34" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="139" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="43" t="s">
         <v>170</v>
       </c>
-      <c r="D9" s="70" t="s">
+      <c r="D9" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="E9" s="70" t="s">
+      <c r="E9" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="F9" s="66" t="s">
+      <c r="F9" s="36" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="152" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="D10" s="70" t="s">
+      <c r="D10" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="E10" s="70" t="s">
+      <c r="E10" s="40" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="71" t="s">
+      <c r="A11" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="71" t="s">
+      <c r="B11" s="41" t="s">
         <v>144</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="71" t="s">
+      <c r="D11" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="E11" s="71" t="s">
+      <c r="E11" s="41" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="409" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="41" t="s">
         <v>148</v>
       </c>
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="D12" s="71" t="s">
+      <c r="D12" s="41" t="s">
         <v>180</v>
       </c>
-      <c r="E12" s="71" t="s">
+      <c r="E12" s="41" t="s">
         <v>181</v>
       </c>
     </row>
